--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
@@ -2239,7 +2239,23 @@
 &lt;answer&gt;C&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>&lt;answer&gt;(A) A. trash bin&lt;/answer&gt;</t>
+    <t>To determine which object (trash bin, microwave, window, refrigerator) is closest to the chair, we need to analyze the spatial relationships between these objects and the chair in the provided frames. Since the frames are uniformly sampled and show different perspectives, we can infer the relative positions of the objects.
+### Step 1: Identify the chair
+The chair is visible in the third frame (frame 3), which shows a dark-colored table or chair in the foreground, with the kitchen counter and sink in the background. The chair is located near the countertop and appears to be positioned adjacent to the counter.
+### Step 2: Identify the positions of the objects
+From the frames, we can identify the locations of the objects:
+- **Trash bin**: Visible in frame 4, positioned near the countertop, next to the table/chair.
+- **Microwave**: Visible in frame 5, mounted above the stove.
+- **Window**: Visible in frame 7, located above the sink, near the countertop.
+- **Refrigerator**: Visible in frame 1, positioned on the left side of the kitchen, next to the stove.
+### Step 3: Determine proximity to the chair
+- The **trash bin** is located near the table/chair, as seen in frame 4. It is positioned directly adjacent to the chair.
+- The **microwave** is located above the stove, which is to the left of the chair. The microwave is not adjacent to the chair.
+- The **window** is located above the sink, which is to the right of the chair. The window is not adjacent to the chair.
+- The **refrigerator** is located to the left of the stove, which is to the left of the chair. The refrigerator is not adjacent to the chair.
+### Step 4: Conclusion
+Based on the spatial relationships, the **trash bin** is the closest to the chair, as it is positioned directly adjacent to it.
+&lt;answer&gt;(A) A. trash bin&lt;/answer&gt;</t>
   </si>
   <si>
     <t>&lt;answer&gt;(D) D. stool&lt;/answer&gt;</t>
@@ -3769,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>72.46120595932007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3798,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>6.764224290847778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3827,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4.038966417312622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3856,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>6.192481994628906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3885,7 +3901,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>5.177309989929199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3914,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>14.34249806404114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3943,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>5.732113599777222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3972,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.292241811752319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4001,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>5.337183475494385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4030,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>6.830707788467407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4059,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>7.36967396736145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4088,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5.022758960723877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4117,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>5.708567380905151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4146,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>8.47289514541626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4175,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>7.451446294784546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4204,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>3.287075519561768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4233,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>5.611904144287109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4262,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>7.045154809951782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4291,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>6.770818471908569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4320,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>5.389206171035767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4349,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>6.302941083908081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4378,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>3.861121416091919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4407,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>4.917988300323486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4436,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>11.6477837562561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4465,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>6.75697922706604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4494,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>5.753191232681274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4523,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>7.00127124786377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4552,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>4.390761613845825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4581,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>6.944268465042114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4610,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>4.512821197509766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4639,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>4.722893238067627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4668,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>4.147605895996094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4697,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>10.10362458229065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4726,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>4.322758913040161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4755,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>12.72012805938721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4784,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>5.35008430480957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4813,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>4.499883651733398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4842,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>4.04980206489563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4871,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>5.660002708435059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4900,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>22.2926812171936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4929,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>7.026780128479004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4958,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>5.124446630477905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4987,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>9.39903450012207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5016,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4.713916301727295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5045,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>6.808764219284058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5074,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>6.491832494735718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5103,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>4.674489259719849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5132,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>4.207973480224609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5161,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4.592246532440186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5190,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>6.355004549026489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5219,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>14.42094159126282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5248,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>5.436092376708984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5277,7 +5293,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>5.108119487762451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5306,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>7.266083955764771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5335,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>4.54459285736084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5364,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>24.1799898147583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5393,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>7.361079216003418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5422,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>14.94310688972473</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5451,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>8.226422786712646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5480,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>9.9989333152771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5509,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>7.452245712280273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5538,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>3.509290933609009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5567,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>5.08720064163208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5596,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>4.039793968200684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5625,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>3.338060140609741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5654,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>8.198148250579834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5683,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>19.35645961761475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5712,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>21.24439191818237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5741,7 +5757,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>30.30130410194397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5770,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>5.351472854614258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5799,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>5.300410747528076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5828,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>7.076550245285034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5857,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>48.24724745750427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5886,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>13.61383748054504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5915,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>16.15556168556213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5944,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>14.39626622200012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5973,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>7.047914266586304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6002,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>10.76492547988892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6031,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>8.080447912216187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6060,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>9.380487680435181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6089,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>4.647791624069214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6118,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5.203908920288086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6147,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>4.115804672241211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6176,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>13.95496201515198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6205,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>12.83496403694153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6234,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>4.646174669265747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6263,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>4.283707141876221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6292,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>6.208662271499634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6321,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>9.524457693099976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6350,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>6.887573003768921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6379,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>6.241355180740356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6408,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>8.793614864349365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6437,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>5.141302585601807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6466,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>26.28285193443298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6495,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>9.957084178924561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6524,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>6.492073059082031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6553,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>3.749712467193604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6582,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>3.977126359939575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6611,7 +6627,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>7.948232650756836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6640,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>6.633180618286133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6666,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>4.311981916427612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6695,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>8.528291940689087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6724,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>8.195941209793091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6753,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>9.396546363830566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6782,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>7.279324531555176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6811,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>21.64059233665466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6840,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>43.61760425567627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6869,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>5.174518585205078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6898,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>6.328264951705933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6927,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>12.6544132232666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6956,7 +6972,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>11.71125888824463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6985,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>5.566461563110352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7014,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>9.926771640777588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7043,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>6.632953882217407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7072,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>10.86911368370056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7101,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>16.60693621635437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7130,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>64.7970130443573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7159,7 +7175,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>14.03365802764893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7188,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>5.011625528335571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7217,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>6.505228757858276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7246,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>6.387232780456543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7275,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>5.23821496963501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7304,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>7.231094121932983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7333,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>7.059817314147949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7362,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>5.987102031707764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7391,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>10.23981356620789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7420,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>12.88651704788208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7449,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="I129">
-        <v>5.151494026184082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7478,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>6.147826433181763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7507,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>10.71692252159119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7536,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>10.41640210151672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7565,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>13.24668025970459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7594,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>7.408410787582397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7623,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>3.833688259124756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7652,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>9.565479755401611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7681,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>5.608312606811523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7710,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>4.348299026489258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7739,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>4.987665414810181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7768,7 +7784,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>1.461496114730835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7797,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>1.637475490570068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7826,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>8.084601640701294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -7855,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>5.277536392211914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -7884,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>2.859438180923462</v>
+        <v>2.946864128112793</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -7913,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>15.98103332519531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -7942,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>8.539616823196411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -7971,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>2.85735011100769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8000,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>3.326503276824951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8029,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>2.76907753944397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8055,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>2.81640362739563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8084,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>11.75277233123779</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8110,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>5.509093999862671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8139,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>4.27820873260498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8165,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>3.952785491943359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8194,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>6.612943649291992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8223,7 +8239,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>17.03263425827026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8252,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="I157">
-        <v>5.182634115219116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8281,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>11.58840394020081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8310,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>6.005695343017578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8339,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>8.208115816116333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8368,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>11.68370771408081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8397,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>6.394815444946289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8426,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>11.91484618186951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8455,7 +8471,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>7.796735048294067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8484,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>5.831609725952148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8513,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="I166">
-        <v>14.89099860191345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8542,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>16.12248587608337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8571,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>5.015346527099609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8600,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>6.716670513153076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8629,7 +8645,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>4.63343071937561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -8658,7 +8674,7 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <v>7.255144119262695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -8687,7 +8703,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>7.99221396446228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -8716,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>4.414049863815308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -8745,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>4.557088851928711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -8774,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>5.990430116653442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -8803,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>10.99626564979553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -8832,7 +8848,7 @@
         <v>0</v>
       </c>
       <c r="I177">
-        <v>6.439382553100586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -8861,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>13.14912343025208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -8890,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>13.23183512687683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -8919,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="I180">
-        <v>13.89662218093872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -8948,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>5.052105665206909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -8977,7 +8993,7 @@
         <v>1</v>
       </c>
       <c r="I182">
-        <v>4.786043643951416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9006,7 +9022,7 @@
         <v>1</v>
       </c>
       <c r="I183">
-        <v>9.157365322113037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9035,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>8.198623657226562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9064,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>2.189337015151978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9093,7 +9109,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>12.64158058166504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9122,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>6.476953268051147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9151,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>7.282856464385986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9177,7 +9193,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>6.825087547302246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9206,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="I190">
-        <v>18.26601791381836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9235,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>9.725859642028809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9264,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>19.05315327644348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9293,7 +9309,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>8.834703207015991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9322,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>2.615036964416504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9351,7 +9367,7 @@
         <v>1</v>
       </c>
       <c r="I195">
-        <v>18.92538499832153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9380,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>5.737663745880127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9409,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>9.911573171615601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9438,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>10.28456163406372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9467,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>19.03089213371277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9496,7 +9512,7 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>6.950775146484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9525,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>2.527291297912598</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
